--- a/#SB19_anonymized.xlsx
+++ b/#SB19_anonymized.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11633,7 +11633,7 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16739,7 +16739,7 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16785,7 +16785,7 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16831,7 +16831,7 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22546,7 +22546,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22592,7 +22592,7 @@
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22684,7 +22684,7 @@
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22731,7 +22731,7 @@
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22777,7 +22777,7 @@
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22868,7 +22868,7 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22912,7 +22912,7 @@
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22956,7 +22956,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23001,7 +23001,7 @@
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
